--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ241"/>
+  <dimension ref="A1:AZ243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26951,10 +26951,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>134797963</v>
+        <v>136656184</v>
       </c>
       <c r="B203" t="n">
-        <v>56861</v>
+        <v>56864</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -26962,36 +26962,28 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N203" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -27003,10 +26995,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>560991</v>
+        <v>560963</v>
       </c>
       <c r="R203" t="n">
-        <v>6627590</v>
+        <v>6627478</v>
       </c>
       <c r="S203" t="n">
         <v>25</v>
@@ -27033,27 +27025,27 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>23:59</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
+          <t>Registrerad med autobox (384 kHz) i övergångszon mellan skogsmiljö och mosse. Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid ca 20:30-tiden och 21:30-tiden den 14 september, med hög klassificeringssäkerhet..</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -27072,7 +27064,7 @@
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+          <t>Olikåldrig tall- och barrdominerad i övergångszon mot mosse.Inslag av löv.I närheten finns en block/stenröse.</t>
         </is>
       </c>
       <c r="AT203" t="inlineStr"/>
@@ -27089,13 +27081,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134797963</t>
+          <t>https://artportalen.se/Sighting/136656184</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>135221801</v>
+        <v>134797963</v>
       </c>
       <c r="B204" t="n">
         <v>56861</v>
@@ -27143,14 +27135,14 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>561104</v>
+        <v>560991</v>
       </c>
       <c r="R204" t="n">
-        <v>6627571</v>
+        <v>6627590</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -27177,27 +27169,27 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>23:59</t>
         </is>
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Brunlångöra registrerades återkommande under perioden 15–17 juli med hög klassificeringssäkerhet (upp till 0,95). Fynden visar att arten regelbundet använder området.</t>
+          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27211,12 +27203,12 @@
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
         </is>
       </c>
       <c r="AT204" t="inlineStr"/>
@@ -27233,16 +27225,16 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135221801</t>
+          <t>https://artportalen.se/Sighting/134797963</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>135605416</v>
+        <v>135221801</v>
       </c>
       <c r="B205" t="n">
-        <v>56864</v>
+        <v>56861</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -27267,15 +27259,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -27287,10 +27283,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>561299</v>
+        <v>561104</v>
       </c>
       <c r="R205" t="n">
-        <v>6627804</v>
+        <v>6627571</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -27317,27 +27313,27 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Brun långöra registrerades vid flera tillfällen under inventeringsperioden, främst omkring midnatt och under de tidiga morgontimmarna. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
+          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Brunlångöra registrerades återkommande under perioden 15–17 juli med hög klassificeringssäkerhet (upp till 0,95). Fynden visar att arten regelbundet använder området.</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -27351,12 +27347,12 @@
       </c>
       <c r="AH205" t="inlineStr">
         <is>
-          <t>Hällmarksblandskog</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>Myrholme med öppet sumpskogsparti</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
         </is>
       </c>
       <c r="AT205" t="inlineStr"/>
@@ -27373,16 +27369,16 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135605416</t>
+          <t>https://artportalen.se/Sighting/135221801</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>136014962</v>
+        <v>135605416</v>
       </c>
       <c r="B206" t="n">
-        <v>56887</v>
+        <v>56864</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -27423,14 +27419,14 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>560990</v>
+        <v>561299</v>
       </c>
       <c r="R206" t="n">
-        <v>6627589</v>
+        <v>6627804</v>
       </c>
       <c r="S206" t="n">
         <v>25</v>
@@ -27457,17 +27453,17 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
@@ -27477,7 +27473,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Registrerad vid upprepade tillfällen med autobox (384 kHz) under nätterna mellan 16–19 augusti, med registreringar från sen kväll till efter midnatt (ca kl. 22:45–02:34). Inspelningarna analyserades med BTO Acoustic Pipeline och klassificerades som brunlångöra med hög sannolikhet.</t>
+          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Brun långöra registrerades vid flera tillfällen under inventeringsperioden, främst omkring midnatt och under de tidiga morgontimmarna. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -27491,12 +27487,12 @@
       </c>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Hällmarksblandskog</t>
         </is>
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>Övergångszon (ekoton) mellan barrskog och öppen mosse.</t>
+          <t>Myrholme med öppet sumpskogsparti</t>
         </is>
       </c>
       <c r="AT206" t="inlineStr"/>
@@ -27513,13 +27509,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136014962</t>
+          <t>https://artportalen.se/Sighting/135605416</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>136171108</v>
+        <v>136014962</v>
       </c>
       <c r="B207" t="n">
         <v>56887</v>
@@ -27563,14 +27559,14 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>561157</v>
+        <v>560990</v>
       </c>
       <c r="R207" t="n">
-        <v>6627778</v>
+        <v>6627589</v>
       </c>
       <c r="S207" t="n">
         <v>25</v>
@@ -27597,17 +27593,17 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
@@ -27617,7 +27613,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Registrerad med autobox (384 kHz) i skogen på myrholme öster om Salsmossen. Inspelningarna analyserades med BTO Acoustic Pipeline. Brunlångöra registrerades vid upprepade tillfällen under natten 22–23 augusti, med hög klassificeringssäkerhet.</t>
+          <t>Registrerad vid upprepade tillfällen med autobox (384 kHz) under nätterna mellan 16–19 augusti, med registreringar från sen kväll till efter midnatt (ca kl. 22:45–02:34). Inspelningarna analyserades med BTO Acoustic Pipeline och klassificerades som brunlångöra med hög sannolikhet.</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -27636,7 +27632,7 @@
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>Olikåldig, tallpräglad barrblandskog på myrholme intill mosse, med inslag av gran och björk samt riklig underväxt.</t>
+          <t>Övergångszon (ekoton) mellan barrskog och öppen mosse.</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr"/>
@@ -27653,16 +27649,16 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136171108</t>
+          <t>https://artportalen.se/Sighting/136014962</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>91949709</v>
+        <v>136171108</v>
       </c>
       <c r="B208" t="n">
-        <v>56522</v>
+        <v>56887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -27670,50 +27666,47 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>206004</v>
+        <v>206002</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Skogsmursvägen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>561067</v>
+        <v>561157</v>
       </c>
       <c r="R208" t="n">
-        <v>6627551</v>
+        <v>6627778</v>
       </c>
       <c r="S208" t="n">
         <v>25</v>
@@ -27740,27 +27733,27 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Sprang över Skogsmursvägen  helvit</t>
+          <t>Registrerad med autobox (384 kHz) i skogen på myrholme öster om Salsmossen. Inspelningarna analyserades med BTO Acoustic Pipeline. Brunlångöra registrerades vid upprepade tillfällen under natten 22–23 augusti, med hög klassificeringssäkerhet.</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -27771,6 +27764,16 @@
       </c>
       <c r="AG208" t="b">
         <v>0</v>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>Olikåldig, tallpräglad barrblandskog på myrholme intill mosse, med inslag av gran och björk samt riklig underväxt.</t>
+        </is>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
@@ -27786,16 +27789,16 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91949709</t>
+          <t>https://artportalen.se/Sighting/136171108</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>135589893</v>
+        <v>136656321</v>
       </c>
       <c r="B209" t="n">
-        <v>56713</v>
+        <v>56887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -27803,16 +27806,16 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>206046</v>
+        <v>206002</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -27820,41 +27823,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>561272</v>
+        <v>560963</v>
       </c>
       <c r="R209" t="n">
-        <v>6627729</v>
+        <v>6627478</v>
       </c>
       <c r="S209" t="n">
         <v>25</v>
@@ -27881,22 +27873,27 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Registrerad med autobox (384 kHz) i övergångszon mellan skogsmiljö och mosse. Inspelningarna analyserades med BTO Acoustic Pipeline. Brunlångöra  registrerades vid ca 21:40-tiden den 14 september, med hög klassificeringssäkerhet..</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -27910,12 +27907,12 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>Hällmarksbarrskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>Myrholme</t>
+          <t>Olikåldrig tall- och barrdominerad i övergångszon mot mosse.Inslag av löv.I närheten finns en block/stenröse.</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr"/>
@@ -27932,16 +27929,16 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135589893</t>
+          <t>https://artportalen.se/Sighting/136656321</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>135649870</v>
+        <v>91949709</v>
       </c>
       <c r="B210" t="n">
-        <v>56718</v>
+        <v>56522</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -27949,26 +27946,26 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>206046</v>
+        <v>206004</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -27977,22 +27974,22 @@
         </is>
       </c>
       <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursvägen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>561104</v>
+        <v>561067</v>
       </c>
       <c r="R210" t="n">
-        <v>6627266</v>
+        <v>6627551</v>
       </c>
       <c r="S210" t="n">
         <v>25</v>
@@ -28019,27 +28016,27 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>Älgko med fjolårsunge</t>
+          <t>Sprang över Skogsmursvägen  helvit</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -28050,11 +28047,6 @@
       </c>
       <c r="AG210" t="b">
         <v>0</v>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
@@ -28070,38 +28062,38 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135649870</t>
+          <t>https://artportalen.se/Sighting/91949709</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>126415504</v>
+        <v>135589893</v>
       </c>
       <c r="B211" t="n">
-        <v>58817</v>
+        <v>56713</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>208249</v>
+        <v>206046</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -28109,28 +28101,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>561023</v>
+        <v>561272</v>
       </c>
       <c r="R211" t="n">
-        <v>6627575</v>
+        <v>6627729</v>
       </c>
       <c r="S211" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -28154,22 +28157,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -28178,13 +28181,17 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>Myrholme</t>
         </is>
       </c>
       <c r="AT211" t="inlineStr"/>
@@ -28201,71 +28208,70 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126415504</t>
+          <t>https://artportalen.se/Sighting/135589893</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>135660351</v>
+        <v>135649870</v>
       </c>
       <c r="B212" t="n">
-        <v>58852</v>
+        <v>56718</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>208249</v>
+        <v>206046</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K212" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
       <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Skogsmursvägen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>561052</v>
+        <v>561104</v>
       </c>
       <c r="R212" t="n">
-        <v>6627613</v>
+        <v>6627266</v>
       </c>
       <c r="S212" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28289,27 +28295,27 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Hoppandes över vägen. Hoppade sen ner i bäcken.</t>
+          <t>Älgko med fjolårsunge</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -28318,7 +28324,6 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
-      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
@@ -28341,16 +28346,16 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135660351</t>
+          <t>https://artportalen.se/Sighting/135649870</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>118334109</v>
+        <v>126415504</v>
       </c>
       <c r="B213" t="n">
-        <v>99035</v>
+        <v>58817</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -28358,21 +28363,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -28380,21 +28385,25 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>561057</v>
+        <v>561023</v>
       </c>
       <c r="R213" t="n">
-        <v>6627592</v>
+        <v>6627575</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -28421,22 +28430,22 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -28445,12 +28454,13 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT213" t="inlineStr"/>
@@ -28467,16 +28477,16 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118334109</t>
+          <t>https://artportalen.se/Sighting/126415504</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>126416641</v>
+        <v>135660351</v>
       </c>
       <c r="B214" t="n">
-        <v>99035</v>
+        <v>58852</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -28484,21 +28494,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -28506,24 +28516,32 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursvägen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>561018</v>
+        <v>561052</v>
       </c>
       <c r="R214" t="n">
-        <v>6627875</v>
+        <v>6627613</v>
       </c>
       <c r="S214" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -28547,22 +28565,27 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Hoppandes över vägen. Hoppade sen ner i bäcken.</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -28571,6 +28594,7 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
+      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -28593,16 +28617,16 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126416641</t>
+          <t>https://artportalen.se/Sighting/135660351</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>135071078</v>
+        <v>118334109</v>
       </c>
       <c r="B215" t="n">
-        <v>99186</v>
+        <v>99035</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -28629,12 +28653,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -28644,17 +28663,17 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>561117</v>
+        <v>561057</v>
       </c>
       <c r="R215" t="n">
-        <v>6627574</v>
+        <v>6627592</v>
       </c>
       <c r="S215" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -28678,22 +28697,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -28707,7 +28726,7 @@
       </c>
       <c r="AH215" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT215" t="inlineStr"/>
@@ -28724,16 +28743,16 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071078</t>
+          <t>https://artportalen.se/Sighting/118334109</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>135147368</v>
+        <v>126416641</v>
       </c>
       <c r="B216" t="n">
-        <v>99186</v>
+        <v>99035</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -28763,11 +28782,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K216" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -28775,17 +28789,17 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>561051</v>
+        <v>561018</v>
       </c>
       <c r="R216" t="n">
-        <v>6627607</v>
+        <v>6627875</v>
       </c>
       <c r="S216" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -28809,22 +28823,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -28835,6 +28849,11 @@
       </c>
       <c r="AG216" t="b">
         <v>0</v>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
@@ -28850,13 +28869,13 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147368</t>
+          <t>https://artportalen.se/Sighting/126416641</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>135147426</v>
+        <v>135071078</v>
       </c>
       <c r="B217" t="n">
         <v>99186</v>
@@ -28886,7 +28905,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -28896,17 +28920,17 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>561010</v>
+        <v>561117</v>
       </c>
       <c r="R217" t="n">
-        <v>6627744</v>
+        <v>6627574</v>
       </c>
       <c r="S217" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -28930,22 +28954,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -28959,7 +28983,7 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr"/>
@@ -28976,13 +29000,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147426</t>
+          <t>https://artportalen.se/Sighting/135071078</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>135147597</v>
+        <v>135147368</v>
       </c>
       <c r="B218" t="n">
         <v>99186</v>
@@ -29012,7 +29036,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -29031,13 +29055,13 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>561003</v>
+        <v>561051</v>
       </c>
       <c r="R218" t="n">
-        <v>6627860</v>
+        <v>6627607</v>
       </c>
       <c r="S218" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -29066,7 +29090,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -29076,7 +29100,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -29087,11 +29111,6 @@
       </c>
       <c r="AG218" t="b">
         <v>0</v>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
@@ -29107,13 +29126,13 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147597</t>
+          <t>https://artportalen.se/Sighting/135147368</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>135147621</v>
+        <v>135147426</v>
       </c>
       <c r="B219" t="n">
         <v>99186</v>
@@ -29143,12 +29162,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -29158,17 +29172,17 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>561005</v>
+        <v>561010</v>
       </c>
       <c r="R219" t="n">
-        <v>6627859</v>
+        <v>6627744</v>
       </c>
       <c r="S219" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29197,7 +29211,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -29207,7 +29221,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29238,68 +29252,68 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147621</t>
+          <t>https://artportalen.se/Sighting/135147426</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>116192832</v>
+        <v>135147597</v>
       </c>
       <c r="B220" t="n">
-        <v>99118</v>
+        <v>99186</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>561001</v>
+        <v>561003</v>
       </c>
       <c r="R220" t="n">
-        <v>6627609</v>
+        <v>6627860</v>
       </c>
       <c r="S220" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -29323,22 +29337,22 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29352,7 +29366,7 @@
       </c>
       <c r="AH220" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT220" t="inlineStr"/>
@@ -29369,38 +29383,38 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116192832</t>
+          <t>https://artportalen.se/Sighting/135147597</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>116196922</v>
+        <v>135147621</v>
       </c>
       <c r="B221" t="n">
-        <v>99118</v>
+        <v>99186</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -29410,29 +29424,27 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>561103</v>
+        <v>561005</v>
       </c>
       <c r="R221" t="n">
-        <v>6627492</v>
+        <v>6627859</v>
       </c>
       <c r="S221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29456,22 +29468,22 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -29480,7 +29492,6 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -29503,13 +29514,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116196922</t>
+          <t>https://artportalen.se/Sighting/135147621</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>116377628</v>
+        <v>116192832</v>
       </c>
       <c r="B222" t="n">
         <v>99118</v>
@@ -29552,22 +29563,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr"/>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>560998</v>
+        <v>561001</v>
       </c>
       <c r="R222" t="n">
-        <v>6627569</v>
+        <v>6627609</v>
       </c>
       <c r="S222" t="n">
         <v>1</v>
@@ -29594,22 +29599,22 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -29618,7 +29623,6 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
-      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>
@@ -29641,13 +29645,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116377628</t>
+          <t>https://artportalen.se/Sighting/116192832</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>123329692</v>
+        <v>116196922</v>
       </c>
       <c r="B223" t="n">
         <v>99118</v>
@@ -29677,12 +29681,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -29691,24 +29695,20 @@
         </is>
       </c>
       <c r="L223" t="inlineStr"/>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>561099</v>
+        <v>561103</v>
       </c>
       <c r="R223" t="n">
         <v>6627492</v>
       </c>
       <c r="S223" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -29732,12 +29732,22 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -29755,11 +29765,6 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AI223" t="inlineStr">
-        <is>
-          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
-        </is>
-      </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
@@ -29774,16 +29779,16 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123329692</t>
+          <t>https://artportalen.se/Sighting/116196922</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>132660822</v>
+        <v>116377628</v>
       </c>
       <c r="B224" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -29810,12 +29815,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -29823,19 +29828,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>560999</v>
+        <v>560998</v>
       </c>
       <c r="R224" t="n">
-        <v>6627568</v>
+        <v>6627569</v>
       </c>
       <c r="S224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -29859,27 +29870,22 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -29888,6 +29894,7 @@
       <c r="AE224" t="b">
         <v>0</v>
       </c>
+      <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
         <v>0</v>
       </c>
@@ -29910,54 +29917,74 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132660822</t>
+          <t>https://artportalen.se/Sighting/116377628</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>4221674</v>
+        <v>123329692</v>
       </c>
       <c r="B225" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Murmossen, Ramnäs sn, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>561035</v>
+        <v>561099</v>
       </c>
       <c r="R225" t="n">
-        <v>6627874</v>
+        <v>6627492</v>
       </c>
       <c r="S225" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -29981,12 +30008,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -29995,76 +30022,96 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
+      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
       </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>Tallskog/moränmark</t>
+          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
         </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4221674</t>
+          <t>https://artportalen.se/Sighting/123329692</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>4225188</v>
+        <v>132660822</v>
       </c>
       <c r="B226" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Salsmossen SV, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>561108</v>
+        <v>560999</v>
       </c>
       <c r="R226" t="n">
-        <v>6627497</v>
+        <v>6627568</v>
       </c>
       <c r="S226" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -30088,17 +30135,27 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>sparsam</t>
+          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -30110,32 +30167,32 @@
       <c r="AG226" t="b">
         <v>0</v>
       </c>
-      <c r="AI226" t="inlineStr">
-        <is>
-          <t>Barrblandskog, inslag av björk</t>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4225188</t>
+          <t>https://artportalen.se/Sighting/132660822</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>99086346</v>
+        <v>4221674</v>
       </c>
       <c r="B227" t="n">
         <v>97983</v>
@@ -30164,27 +30221,19 @@
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>561003</v>
+        <v>561035</v>
       </c>
       <c r="R227" t="n">
-        <v>6627635</v>
+        <v>6627874</v>
       </c>
       <c r="S227" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -30208,12 +30257,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -30222,31 +30271,35 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>Tallskog/moränmark</t>
+        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99086346</t>
+          <t>https://artportalen.se/Sighting/4221674</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>104578243</v>
+        <v>4225188</v>
       </c>
       <c r="B228" t="n">
         <v>97983</v>
@@ -30275,27 +30328,19 @@
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Salsmossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>560987</v>
+        <v>561108</v>
       </c>
       <c r="R228" t="n">
-        <v>6627629</v>
+        <v>6627497</v>
       </c>
       <c r="S228" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30319,12 +30364,17 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2012-07-10</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2012-07-10</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>sparsam</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -30333,36 +30383,35 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104578243</t>
+          <t>https://artportalen.se/Sighting/4225188</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>116192263</v>
+        <v>99086346</v>
       </c>
       <c r="B229" t="n">
         <v>97983</v>
@@ -30390,26 +30439,25 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>560991</v>
+        <v>561003</v>
       </c>
       <c r="R229" t="n">
-        <v>6627626</v>
+        <v>6627635</v>
       </c>
       <c r="S229" t="n">
         <v>5</v>
@@ -30436,22 +30484,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30460,13 +30498,9 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
+      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
@@ -30482,13 +30516,13 @@
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116192263</t>
+          <t>https://artportalen.se/Sighting/99086346</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>126413111</v>
+        <v>104578243</v>
       </c>
       <c r="B230" t="n">
         <v>97983</v>
@@ -30516,29 +30550,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>561017</v>
+        <v>560987</v>
       </c>
       <c r="R230" t="n">
-        <v>6627814</v>
+        <v>6627629</v>
       </c>
       <c r="S230" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -30562,22 +30595,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -30586,8 +30609,14 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
+      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
@@ -30603,13 +30632,13 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126413111</t>
+          <t>https://artportalen.se/Sighting/104578243</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>126413356</v>
+        <v>116192263</v>
       </c>
       <c r="B231" t="n">
         <v>97983</v>
@@ -30639,7 +30668,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -30649,17 +30678,17 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>561013</v>
+        <v>560991</v>
       </c>
       <c r="R231" t="n">
-        <v>6627677</v>
+        <v>6627626</v>
       </c>
       <c r="S231" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -30683,22 +30712,22 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -30729,13 +30758,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126413356</t>
+          <t>https://artportalen.se/Sighting/116192263</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>126416592</v>
+        <v>126413111</v>
       </c>
       <c r="B232" t="n">
         <v>97983</v>
@@ -30765,7 +30794,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -30779,13 +30808,13 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>561027</v>
+        <v>561017</v>
       </c>
       <c r="R232" t="n">
-        <v>6627858</v>
+        <v>6627814</v>
       </c>
       <c r="S232" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -30814,7 +30843,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -30824,7 +30853,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -30850,13 +30879,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126416592</t>
+          <t>https://artportalen.se/Sighting/126413111</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128162622</v>
+        <v>126413356</v>
       </c>
       <c r="B233" t="n">
         <v>97983</v>
@@ -30900,10 +30929,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>561012</v>
+        <v>561013</v>
       </c>
       <c r="R233" t="n">
-        <v>6627671</v>
+        <v>6627677</v>
       </c>
       <c r="S233" t="n">
         <v>1</v>
@@ -30930,22 +30959,22 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -30976,16 +31005,16 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128162622</t>
+          <t>https://artportalen.se/Sighting/126413356</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>133764984</v>
+        <v>126416592</v>
       </c>
       <c r="B234" t="n">
-        <v>98060</v>
+        <v>97983</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -31012,7 +31041,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -31022,17 +31051,17 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>561227</v>
+        <v>561027</v>
       </c>
       <c r="R234" t="n">
-        <v>6627267</v>
+        <v>6627858</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -31056,22 +31085,22 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -31082,11 +31111,6 @@
       </c>
       <c r="AG234" t="b">
         <v>0</v>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
@@ -31102,16 +31126,16 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133764984</t>
+          <t>https://artportalen.se/Sighting/126416592</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>136175493</v>
+        <v>128162622</v>
       </c>
       <c r="B235" t="n">
-        <v>98204</v>
+        <v>97983</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -31138,7 +31162,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -31146,26 +31170,19 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>561037</v>
+        <v>561012</v>
       </c>
       <c r="R235" t="n">
-        <v>6627842</v>
+        <v>6627671</v>
       </c>
       <c r="S235" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -31189,22 +31206,22 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -31213,7 +31230,6 @@
       <c r="AE235" t="b">
         <v>0</v>
       </c>
-      <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="b">
         <v>0</v>
       </c>
@@ -31236,16 +31252,16 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136175493</t>
+          <t>https://artportalen.se/Sighting/128162622</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>112959278</v>
+        <v>133764984</v>
       </c>
       <c r="B236" t="n">
-        <v>97986</v>
+        <v>98060</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -31253,16 +31269,16 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -31270,28 +31286,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>561019</v>
+        <v>561227</v>
       </c>
       <c r="R236" t="n">
-        <v>6627490</v>
+        <v>6627267</v>
       </c>
       <c r="S236" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -31315,12 +31332,22 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -31329,9 +31356,13 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
-      <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="b">
         <v>0</v>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
@@ -31347,16 +31378,16 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112959278</t>
+          <t>https://artportalen.se/Sighting/133764984</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>134063381</v>
+        <v>136175493</v>
       </c>
       <c r="B237" t="n">
-        <v>99472</v>
+        <v>98204</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -31364,16 +31395,16 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>222812</v>
+        <v>221945</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -31381,10 +31412,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -31393,13 +31435,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>560964</v>
+        <v>561037</v>
       </c>
       <c r="R237" t="n">
-        <v>6627632</v>
+        <v>6627842</v>
       </c>
       <c r="S237" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -31423,22 +31465,22 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -31447,6 +31489,7 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
+      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
       </c>
@@ -31469,16 +31512,16 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134063381</t>
+          <t>https://artportalen.se/Sighting/136175493</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>5979250</v>
+        <v>112959278</v>
       </c>
       <c r="B238" t="n">
-        <v>99038</v>
+        <v>97986</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -31486,44 +31529,42 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>560984</v>
+        <v>561019</v>
       </c>
       <c r="R238" t="n">
-        <v>6627735</v>
+        <v>6627490</v>
       </c>
       <c r="S238" t="n">
         <v>25</v>
@@ -31550,12 +31591,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -31564,38 +31605,34 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
+      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
-        </is>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979250</t>
+          <t>https://artportalen.se/Sighting/112959278</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>5979251</v>
+        <v>134063381</v>
       </c>
       <c r="B239" t="n">
-        <v>99038</v>
+        <v>99472</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -31603,47 +31640,42 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>223597</v>
+        <v>222812</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>560967</v>
+        <v>560964</v>
       </c>
       <c r="R239" t="n">
-        <v>6627698</v>
+        <v>6627632</v>
       </c>
       <c r="S239" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -31667,12 +31699,22 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -31684,32 +31726,32 @@
       <c r="AG239" t="b">
         <v>0</v>
       </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979251</t>
+          <t>https://artportalen.se/Sighting/134063381</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>5979254</v>
+        <v>5979250</v>
       </c>
       <c r="B240" t="n">
         <v>99038</v>
@@ -31735,7 +31777,7 @@
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -31754,10 +31796,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>560937</v>
+        <v>560984</v>
       </c>
       <c r="R240" t="n">
-        <v>6627972</v>
+        <v>6627735</v>
       </c>
       <c r="S240" t="n">
         <v>25</v>
@@ -31820,13 +31862,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979254</t>
+          <t>https://artportalen.se/Sighting/5979250</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>5979255</v>
+        <v>5979251</v>
       </c>
       <c r="B241" t="n">
         <v>99038</v>
@@ -31852,7 +31894,7 @@
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -31871,10 +31913,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>560943</v>
+        <v>560967</v>
       </c>
       <c r="R241" t="n">
-        <v>6627939</v>
+        <v>6627698</v>
       </c>
       <c r="S241" t="n">
         <v>25</v>
@@ -31936,6 +31978,240 @@
       </c>
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5979251</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>5979254</v>
+      </c>
+      <c r="B242" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>560937</v>
+      </c>
+      <c r="R242" t="n">
+        <v>6627972</v>
+      </c>
+      <c r="S242" t="n">
+        <v>25</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT242" t="inlineStr"/>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5979254</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>5979255</v>
+      </c>
+      <c r="B243" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>560943</v>
+      </c>
+      <c r="R243" t="n">
+        <v>6627939</v>
+      </c>
+      <c r="S243" t="n">
+        <v>25</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT243" t="inlineStr"/>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5979255</t>
         </is>
@@ -32183,6 +32459,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>136117990</v>
       </c>
       <c r="B37" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>136175493</v>
       </c>
       <c r="B237" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>136117990</v>
       </c>
       <c r="B37" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>136175493</v>
       </c>
       <c r="B237" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>136117990</v>
       </c>
       <c r="B37" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>136172601</v>
       </c>
       <c r="B75" t="n">
-        <v>56880</v>
+        <v>56882</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>136168846</v>
       </c>
       <c r="B159" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>136168858</v>
       </c>
       <c r="B164" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>136171058</v>
       </c>
       <c r="B202" t="n">
-        <v>56864</v>
+        <v>56866</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>136656184</v>
       </c>
       <c r="B203" t="n">
-        <v>56864</v>
+        <v>56866</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>136171108</v>
       </c>
       <c r="B208" t="n">
-        <v>56887</v>
+        <v>56889</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>136656321</v>
       </c>
       <c r="B209" t="n">
-        <v>56887</v>
+        <v>56889</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>136175493</v>
       </c>
       <c r="B237" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -31506,7 +31506,7 @@
         <v>136175493</v>
       </c>
       <c r="B238" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ244"/>
+  <dimension ref="A1:AZ246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27206,10 +27206,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>134797963</v>
+        <v>136948211</v>
       </c>
       <c r="B205" t="n">
-        <v>56861</v>
+        <v>56866</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -27217,23 +27217,19 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>1</t>
@@ -27246,7 +27242,11 @@
       </c>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N205" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -27258,10 +27258,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>560991</v>
+        <v>560945</v>
       </c>
       <c r="R205" t="n">
-        <v>6627590</v>
+        <v>6627981</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -27288,27 +27288,27 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>23:59</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
+          <t>Registrerad med autobox (384 kHz) i öppen glänta i tallskog i kantzoon mot Murmossen. Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid 19:44-tiden med hög klassificeringssäkerhet.</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -27327,7 +27327,7 @@
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT205" t="inlineStr"/>
@@ -27344,13 +27344,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134797963</t>
+          <t>https://artportalen.se/Sighting/136948211</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>135221801</v>
+        <v>134797963</v>
       </c>
       <c r="B206" t="n">
         <v>56861</v>
@@ -27398,14 +27398,14 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>561104</v>
+        <v>560991</v>
       </c>
       <c r="R206" t="n">
-        <v>6627571</v>
+        <v>6627590</v>
       </c>
       <c r="S206" t="n">
         <v>25</v>
@@ -27432,27 +27432,27 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>23:59</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Brunlångöra registrerades återkommande under perioden 15–17 juli med hög klassificeringssäkerhet (upp till 0,95). Fynden visar att arten regelbundet använder området.</t>
+          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -27466,12 +27466,12 @@
       </c>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
         </is>
       </c>
       <c r="AT206" t="inlineStr"/>
@@ -27488,16 +27488,16 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135221801</t>
+          <t>https://artportalen.se/Sighting/134797963</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>135605416</v>
+        <v>135221801</v>
       </c>
       <c r="B207" t="n">
-        <v>56864</v>
+        <v>56861</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -27522,15 +27522,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -27542,10 +27546,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>561299</v>
+        <v>561104</v>
       </c>
       <c r="R207" t="n">
-        <v>6627804</v>
+        <v>6627571</v>
       </c>
       <c r="S207" t="n">
         <v>25</v>
@@ -27572,27 +27576,27 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Brun långöra registrerades vid flera tillfällen under inventeringsperioden, främst omkring midnatt och under de tidiga morgontimmarna. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
+          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Brunlångöra registrerades återkommande under perioden 15–17 juli med hög klassificeringssäkerhet (upp till 0,95). Fynden visar att arten regelbundet använder området.</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -27606,12 +27610,12 @@
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>Hällmarksblandskog</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>Myrholme med öppet sumpskogsparti</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr"/>
@@ -27628,16 +27632,16 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135605416</t>
+          <t>https://artportalen.se/Sighting/135221801</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>136014962</v>
+        <v>135605416</v>
       </c>
       <c r="B208" t="n">
-        <v>56887</v>
+        <v>56864</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -27678,14 +27682,14 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>560990</v>
+        <v>561299</v>
       </c>
       <c r="R208" t="n">
-        <v>6627589</v>
+        <v>6627804</v>
       </c>
       <c r="S208" t="n">
         <v>25</v>
@@ -27712,17 +27716,17 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
@@ -27732,7 +27736,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Registrerad vid upprepade tillfällen med autobox (384 kHz) under nätterna mellan 16–19 augusti, med registreringar från sen kväll till efter midnatt (ca kl. 22:45–02:34). Inspelningarna analyserades med BTO Acoustic Pipeline och klassificerades som brunlångöra med hög sannolikhet.</t>
+          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Brun långöra registrerades vid flera tillfällen under inventeringsperioden, främst omkring midnatt och under de tidiga morgontimmarna. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -27746,12 +27750,12 @@
       </c>
       <c r="AH208" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Hällmarksblandskog</t>
         </is>
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>Övergångszon (ekoton) mellan barrskog och öppen mosse.</t>
+          <t>Myrholme med öppet sumpskogsparti</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr"/>
@@ -27768,16 +27772,16 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136014962</t>
+          <t>https://artportalen.se/Sighting/135605416</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>136171108</v>
+        <v>136014962</v>
       </c>
       <c r="B209" t="n">
-        <v>56889</v>
+        <v>56887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -27818,14 +27822,14 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>561157</v>
+        <v>560990</v>
       </c>
       <c r="R209" t="n">
-        <v>6627778</v>
+        <v>6627589</v>
       </c>
       <c r="S209" t="n">
         <v>25</v>
@@ -27852,17 +27856,17 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
@@ -27872,7 +27876,7 @@
       </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>Registrerad med autobox (384 kHz) i skogen på myrholme öster om Salsmossen. Inspelningarna analyserades med BTO Acoustic Pipeline. Brunlångöra registrerades vid upprepade tillfällen under natten 22–23 augusti, med hög klassificeringssäkerhet.</t>
+          <t>Registrerad vid upprepade tillfällen med autobox (384 kHz) under nätterna mellan 16–19 augusti, med registreringar från sen kväll till efter midnatt (ca kl. 22:45–02:34). Inspelningarna analyserades med BTO Acoustic Pipeline och klassificerades som brunlångöra med hög sannolikhet.</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -27891,7 +27895,7 @@
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>Olikåldig, tallpräglad barrblandskog på myrholme intill mosse, med inslag av gran och björk samt riklig underväxt.</t>
+          <t>Övergångszon (ekoton) mellan barrskog och öppen mosse.</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr"/>
@@ -27908,13 +27912,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136171108</t>
+          <t>https://artportalen.se/Sighting/136014962</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>136656321</v>
+        <v>136171108</v>
       </c>
       <c r="B210" t="n">
         <v>56889</v>
@@ -27958,14 +27962,14 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>560963</v>
+        <v>561157</v>
       </c>
       <c r="R210" t="n">
-        <v>6627478</v>
+        <v>6627778</v>
       </c>
       <c r="S210" t="n">
         <v>25</v>
@@ -27992,7 +27996,7 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
@@ -28002,17 +28006,17 @@
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>Registrerad med autobox (384 kHz) i övergångszon mellan skogsmiljö och mosse. Inspelningarna analyserades med BTO Acoustic Pipeline. Brunlångöra  registrerades vid ca 21:40-tiden den 14 september, med hög klassificeringssäkerhet..</t>
+          <t>Registrerad med autobox (384 kHz) i skogen på myrholme öster om Salsmossen. Inspelningarna analyserades med BTO Acoustic Pipeline. Brunlångöra registrerades vid upprepade tillfällen under natten 22–23 augusti, med hög klassificeringssäkerhet.</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -28031,7 +28035,7 @@
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>Olikåldrig tall- och barrdominerad i övergångszon mot mosse.Inslag av löv.I närheten finns en block/stenröse.</t>
+          <t>Olikåldig, tallpräglad barrblandskog på myrholme intill mosse, med inslag av gran och björk samt riklig underväxt.</t>
         </is>
       </c>
       <c r="AT210" t="inlineStr"/>
@@ -28048,16 +28052,16 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136656321</t>
+          <t>https://artportalen.se/Sighting/136171108</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>91949709</v>
+        <v>136656321</v>
       </c>
       <c r="B211" t="n">
-        <v>56522</v>
+        <v>56889</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -28065,50 +28069,47 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>206004</v>
+        <v>206002</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Skogsmursvägen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>561067</v>
+        <v>560963</v>
       </c>
       <c r="R211" t="n">
-        <v>6627551</v>
+        <v>6627478</v>
       </c>
       <c r="S211" t="n">
         <v>25</v>
@@ -28135,27 +28136,27 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>Sprang över Skogsmursvägen  helvit</t>
+          <t>Registrerad med autobox (384 kHz) i övergångszon mellan skogsmiljö och mosse. Inspelningarna analyserades med BTO Acoustic Pipeline. Brunlångöra  registrerades vid ca 21:40-tiden den 14 september, med hög klassificeringssäkerhet..</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -28166,6 +28167,16 @@
       </c>
       <c r="AG211" t="b">
         <v>0</v>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>Olikåldrig tall- och barrdominerad i övergångszon mot mosse.Inslag av löv.I närheten finns en block/stenröse.</t>
+        </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
@@ -28181,16 +28192,16 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91949709</t>
+          <t>https://artportalen.se/Sighting/136656321</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>135589893</v>
+        <v>91949709</v>
       </c>
       <c r="B212" t="n">
-        <v>56713</v>
+        <v>56522</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -28198,21 +28209,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>206046</v>
+        <v>206004</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -28225,16 +28236,8 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -28242,14 +28245,14 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursvägen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>561272</v>
+        <v>561067</v>
       </c>
       <c r="R212" t="n">
-        <v>6627729</v>
+        <v>6627551</v>
       </c>
       <c r="S212" t="n">
         <v>25</v>
@@ -28276,22 +28279,27 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Sprang över Skogsmursvägen  helvit</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -28302,16 +28310,6 @@
       </c>
       <c r="AG212" t="b">
         <v>0</v>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>Hällmarksbarrskog</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>Myrholme</t>
-        </is>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
@@ -28327,16 +28325,16 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135589893</t>
+          <t>https://artportalen.se/Sighting/91949709</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>135649870</v>
+        <v>135589893</v>
       </c>
       <c r="B213" t="n">
-        <v>56718</v>
+        <v>56713</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -28363,7 +28361,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -28371,23 +28369,31 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>561104</v>
+        <v>561272</v>
       </c>
       <c r="R213" t="n">
-        <v>6627266</v>
+        <v>6627729</v>
       </c>
       <c r="S213" t="n">
         <v>25</v>
@@ -28414,27 +28420,22 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Älgko med fjolårsunge</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -28448,7 +28449,12 @@
       </c>
       <c r="AH213" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>Myrholme</t>
         </is>
       </c>
       <c r="AT213" t="inlineStr"/>
@@ -28465,67 +28471,70 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135649870</t>
+          <t>https://artportalen.se/Sighting/135589893</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>126415504</v>
+        <v>135649870</v>
       </c>
       <c r="B214" t="n">
-        <v>58817</v>
+        <v>56718</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>208249</v>
+        <v>206046</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>561023</v>
+        <v>561104</v>
       </c>
       <c r="R214" t="n">
-        <v>6627575</v>
+        <v>6627266</v>
       </c>
       <c r="S214" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -28549,22 +28558,27 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Älgko med fjolårsunge</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -28573,13 +28587,12 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
-      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT214" t="inlineStr"/>
@@ -28596,16 +28609,16 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126415504</t>
+          <t>https://artportalen.se/Sighting/135649870</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>135660351</v>
+        <v>126415504</v>
       </c>
       <c r="B215" t="n">
-        <v>58852</v>
+        <v>58817</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -28638,26 +28651,22 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Skogsmursvägen, Ramnäs, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>561052</v>
+        <v>561023</v>
       </c>
       <c r="R215" t="n">
-        <v>6627613</v>
+        <v>6627575</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -28684,27 +28693,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>Hoppandes över vägen. Hoppade sen ner i bäcken.</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -28719,7 +28723,7 @@
       </c>
       <c r="AH215" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT215" t="inlineStr"/>
@@ -28736,16 +28740,16 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135660351</t>
+          <t>https://artportalen.se/Sighting/126415504</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>118334109</v>
+        <v>135660351</v>
       </c>
       <c r="B216" t="n">
-        <v>99035</v>
+        <v>58852</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -28753,21 +28757,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -28775,21 +28779,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursvägen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>561057</v>
+        <v>561052</v>
       </c>
       <c r="R216" t="n">
-        <v>6627592</v>
+        <v>6627613</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -28816,22 +28828,27 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>Hoppandes över vägen. Hoppade sen ner i bäcken.</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -28840,6 +28857,7 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
+      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -28862,13 +28880,13 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118334109</t>
+          <t>https://artportalen.se/Sighting/135660351</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>126416641</v>
+        <v>118334109</v>
       </c>
       <c r="B217" t="n">
         <v>99035</v>
@@ -28908,17 +28926,17 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>561018</v>
+        <v>561057</v>
       </c>
       <c r="R217" t="n">
-        <v>6627875</v>
+        <v>6627592</v>
       </c>
       <c r="S217" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -28942,22 +28960,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -28988,16 +29006,16 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126416641</t>
+          <t>https://artportalen.se/Sighting/118334109</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>135071078</v>
+        <v>126416641</v>
       </c>
       <c r="B218" t="n">
-        <v>99186</v>
+        <v>99035</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -29024,12 +29042,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -29039,17 +29052,17 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>561117</v>
+        <v>561018</v>
       </c>
       <c r="R218" t="n">
-        <v>6627574</v>
+        <v>6627875</v>
       </c>
       <c r="S218" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -29073,22 +29086,22 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -29102,7 +29115,7 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT218" t="inlineStr"/>
@@ -29119,13 +29132,13 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071078</t>
+          <t>https://artportalen.se/Sighting/126416641</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>135147368</v>
+        <v>135071078</v>
       </c>
       <c r="B219" t="n">
         <v>99186</v>
@@ -29155,7 +29168,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -29174,13 +29187,13 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>561051</v>
+        <v>561117</v>
       </c>
       <c r="R219" t="n">
-        <v>6627607</v>
+        <v>6627574</v>
       </c>
       <c r="S219" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29204,22 +29217,22 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29230,6 +29243,11 @@
       </c>
       <c r="AG219" t="b">
         <v>0</v>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
@@ -29245,13 +29263,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147368</t>
+          <t>https://artportalen.se/Sighting/135071078</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>135147426</v>
+        <v>135147368</v>
       </c>
       <c r="B220" t="n">
         <v>99186</v>
@@ -29281,7 +29299,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -29291,17 +29314,17 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>561010</v>
+        <v>561051</v>
       </c>
       <c r="R220" t="n">
-        <v>6627744</v>
+        <v>6627607</v>
       </c>
       <c r="S220" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -29330,7 +29353,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -29340,7 +29363,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29351,11 +29374,6 @@
       </c>
       <c r="AG220" t="b">
         <v>0</v>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
@@ -29371,13 +29389,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147426</t>
+          <t>https://artportalen.se/Sighting/135147368</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>135147597</v>
+        <v>135147426</v>
       </c>
       <c r="B221" t="n">
         <v>99186</v>
@@ -29407,12 +29425,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -29422,17 +29435,17 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>561003</v>
+        <v>561010</v>
       </c>
       <c r="R221" t="n">
-        <v>6627860</v>
+        <v>6627744</v>
       </c>
       <c r="S221" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29461,7 +29474,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -29471,7 +29484,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -29485,7 +29498,7 @@
       </c>
       <c r="AH221" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT221" t="inlineStr"/>
@@ -29502,13 +29515,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147597</t>
+          <t>https://artportalen.se/Sighting/135147426</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>135147621</v>
+        <v>135147597</v>
       </c>
       <c r="B222" t="n">
         <v>99186</v>
@@ -29538,7 +29551,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -29557,13 +29570,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>561005</v>
+        <v>561003</v>
       </c>
       <c r="R222" t="n">
-        <v>6627859</v>
+        <v>6627860</v>
       </c>
       <c r="S222" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29592,7 +29605,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -29602,7 +29615,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -29616,7 +29629,7 @@
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr"/>
@@ -29633,38 +29646,38 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147621</t>
+          <t>https://artportalen.se/Sighting/135147597</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>116192832</v>
+        <v>135147621</v>
       </c>
       <c r="B223" t="n">
-        <v>99118</v>
+        <v>99186</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -29674,27 +29687,27 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>561001</v>
+        <v>561005</v>
       </c>
       <c r="R223" t="n">
-        <v>6627609</v>
+        <v>6627859</v>
       </c>
       <c r="S223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -29718,22 +29731,22 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -29764,13 +29777,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116192832</t>
+          <t>https://artportalen.se/Sighting/135147621</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>116196922</v>
+        <v>116192832</v>
       </c>
       <c r="B224" t="n">
         <v>99118</v>
@@ -29813,18 +29826,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>561103</v>
+        <v>561001</v>
       </c>
       <c r="R224" t="n">
-        <v>6627492</v>
+        <v>6627609</v>
       </c>
       <c r="S224" t="n">
         <v>1</v>
@@ -29856,7 +29867,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -29866,7 +29877,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -29875,7 +29886,6 @@
       <c r="AE224" t="b">
         <v>0</v>
       </c>
-      <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
         <v>0</v>
       </c>
@@ -29898,13 +29908,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116196922</t>
+          <t>https://artportalen.se/Sighting/116192832</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>116377628</v>
+        <v>116196922</v>
       </c>
       <c r="B225" t="n">
         <v>99118</v>
@@ -29948,21 +29958,17 @@
         </is>
       </c>
       <c r="L225" t="inlineStr"/>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>560998</v>
+        <v>561103</v>
       </c>
       <c r="R225" t="n">
-        <v>6627569</v>
+        <v>6627492</v>
       </c>
       <c r="S225" t="n">
         <v>1</v>
@@ -29989,22 +29995,22 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -30036,13 +30042,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116377628</t>
+          <t>https://artportalen.se/Sighting/116196922</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>123329692</v>
+        <v>116377628</v>
       </c>
       <c r="B226" t="n">
         <v>99118</v>
@@ -30072,12 +30078,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -30093,17 +30099,17 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>561099</v>
+        <v>560998</v>
       </c>
       <c r="R226" t="n">
-        <v>6627492</v>
+        <v>6627569</v>
       </c>
       <c r="S226" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -30127,12 +30133,22 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -30150,11 +30166,6 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AI226" t="inlineStr">
-        <is>
-          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
-        </is>
-      </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
@@ -30169,16 +30180,16 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123329692</t>
+          <t>https://artportalen.se/Sighting/116377628</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>132660822</v>
+        <v>123329692</v>
       </c>
       <c r="B227" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -30205,7 +30216,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -30218,19 +30229,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>560999</v>
+        <v>561099</v>
       </c>
       <c r="R227" t="n">
-        <v>6627568</v>
+        <v>6627492</v>
       </c>
       <c r="S227" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -30254,27 +30271,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -30283,12 +30285,18 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr"/>
@@ -30305,54 +30313,68 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132660822</t>
+          <t>https://artportalen.se/Sighting/123329692</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>4221674</v>
+        <v>132660822</v>
       </c>
       <c r="B228" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Murmossen, Ramnäs sn, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>561035</v>
+        <v>560999</v>
       </c>
       <c r="R228" t="n">
-        <v>6627874</v>
+        <v>6627568</v>
       </c>
       <c r="S228" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30376,12 +30398,27 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -30393,32 +30430,32 @@
       <c r="AG228" t="b">
         <v>0</v>
       </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>Tallskog/moränmark</t>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4221674</t>
+          <t>https://artportalen.se/Sighting/132660822</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>4225188</v>
+        <v>4221674</v>
       </c>
       <c r="B229" t="n">
         <v>97983</v>
@@ -30449,17 +30486,17 @@
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Salsmossen SV, Vstm</t>
+          <t>Murmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>561108</v>
+        <v>561035</v>
       </c>
       <c r="R229" t="n">
-        <v>6627497</v>
+        <v>6627874</v>
       </c>
       <c r="S229" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30483,17 +30520,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>sparsam</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30507,30 +30539,30 @@
       </c>
       <c r="AI229" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av björk</t>
+          <t>Tallskog/moränmark</t>
         </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4225188</t>
+          <t>https://artportalen.se/Sighting/4221674</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>99086346</v>
+        <v>4225188</v>
       </c>
       <c r="B230" t="n">
         <v>97983</v>
@@ -30559,27 +30591,19 @@
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>561003</v>
+        <v>561108</v>
       </c>
       <c r="R230" t="n">
-        <v>6627635</v>
+        <v>6627497</v>
       </c>
       <c r="S230" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -30603,12 +30627,17 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2012-07-10</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2012-07-10</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>sparsam</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -30617,31 +30646,35 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
-      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
+        </is>
       </c>
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99086346</t>
+          <t>https://artportalen.se/Sighting/4225188</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>104578243</v>
+        <v>99086346</v>
       </c>
       <c r="B231" t="n">
         <v>97983</v>
@@ -30680,17 +30713,17 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>560987</v>
+        <v>561003</v>
       </c>
       <c r="R231" t="n">
-        <v>6627629</v>
+        <v>6627635</v>
       </c>
       <c r="S231" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -30714,12 +30747,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -30732,11 +30765,6 @@
       <c r="AG231" t="b">
         <v>0</v>
       </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
@@ -30751,13 +30779,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104578243</t>
+          <t>https://artportalen.se/Sighting/99086346</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>116192263</v>
+        <v>104578243</v>
       </c>
       <c r="B232" t="n">
         <v>97983</v>
@@ -30785,29 +30813,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>560991</v>
+        <v>560987</v>
       </c>
       <c r="R232" t="n">
-        <v>6627626</v>
+        <v>6627629</v>
       </c>
       <c r="S232" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -30831,22 +30858,12 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -30855,6 +30872,7 @@
       <c r="AE232" t="b">
         <v>0</v>
       </c>
+      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
       </c>
@@ -30877,13 +30895,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116192263</t>
+          <t>https://artportalen.se/Sighting/104578243</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>126413111</v>
+        <v>116192263</v>
       </c>
       <c r="B233" t="n">
         <v>97983</v>
@@ -30913,7 +30931,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -30923,14 +30941,14 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>561017</v>
+        <v>560991</v>
       </c>
       <c r="R233" t="n">
-        <v>6627814</v>
+        <v>6627626</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -30957,22 +30975,22 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -30983,6 +31001,11 @@
       </c>
       <c r="AG233" t="b">
         <v>0</v>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
@@ -30998,13 +31021,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126413111</t>
+          <t>https://artportalen.se/Sighting/116192263</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>126413356</v>
+        <v>126413111</v>
       </c>
       <c r="B234" t="n">
         <v>97983</v>
@@ -31034,7 +31057,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -31044,17 +31067,17 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>561013</v>
+        <v>561017</v>
       </c>
       <c r="R234" t="n">
-        <v>6627677</v>
+        <v>6627814</v>
       </c>
       <c r="S234" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -31083,7 +31106,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -31093,7 +31116,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -31104,11 +31127,6 @@
       </c>
       <c r="AG234" t="b">
         <v>0</v>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
@@ -31124,13 +31142,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126413356</t>
+          <t>https://artportalen.se/Sighting/126413111</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>126416592</v>
+        <v>126413356</v>
       </c>
       <c r="B235" t="n">
         <v>97983</v>
@@ -31170,14 +31188,14 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>561027</v>
+        <v>561013</v>
       </c>
       <c r="R235" t="n">
-        <v>6627858</v>
+        <v>6627677</v>
       </c>
       <c r="S235" t="n">
         <v>1</v>
@@ -31209,7 +31227,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -31219,7 +31237,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -31230,6 +31248,11 @@
       </c>
       <c r="AG235" t="b">
         <v>0</v>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
@@ -31245,13 +31268,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126416592</t>
+          <t>https://artportalen.se/Sighting/126413356</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128162622</v>
+        <v>126416592</v>
       </c>
       <c r="B236" t="n">
         <v>97983</v>
@@ -31291,14 +31314,14 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>561012</v>
+        <v>561027</v>
       </c>
       <c r="R236" t="n">
-        <v>6627671</v>
+        <v>6627858</v>
       </c>
       <c r="S236" t="n">
         <v>1</v>
@@ -31325,22 +31348,22 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -31351,11 +31374,6 @@
       </c>
       <c r="AG236" t="b">
         <v>0</v>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
@@ -31371,16 +31389,16 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128162622</t>
+          <t>https://artportalen.se/Sighting/126416592</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>133764984</v>
+        <v>128162622</v>
       </c>
       <c r="B237" t="n">
-        <v>98060</v>
+        <v>97983</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -31407,7 +31425,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -31417,17 +31435,17 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>561227</v>
+        <v>561012</v>
       </c>
       <c r="R237" t="n">
-        <v>6627267</v>
+        <v>6627671</v>
       </c>
       <c r="S237" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -31451,22 +31469,22 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -31497,16 +31515,16 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133764984</t>
+          <t>https://artportalen.se/Sighting/128162622</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>136175493</v>
+        <v>133764984</v>
       </c>
       <c r="B238" t="n">
-        <v>98215</v>
+        <v>98060</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -31533,7 +31551,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -31541,23 +31559,16 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="N238" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>561037</v>
+        <v>561227</v>
       </c>
       <c r="R238" t="n">
-        <v>6627842</v>
+        <v>6627267</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -31584,22 +31595,22 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -31608,7 +31619,6 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
-      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
@@ -31631,16 +31641,16 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136175493</t>
+          <t>https://artportalen.se/Sighting/133764984</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>112959278</v>
+        <v>136175493</v>
       </c>
       <c r="B239" t="n">
-        <v>97986</v>
+        <v>98215</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -31648,16 +31658,16 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -31665,8 +31675,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr"/>
       <c r="N239" t="inlineStr">
@@ -31676,17 +31694,17 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>561019</v>
+        <v>561037</v>
       </c>
       <c r="R239" t="n">
-        <v>6627490</v>
+        <v>6627842</v>
       </c>
       <c r="S239" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -31710,12 +31728,22 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -31728,6 +31756,11 @@
       <c r="AG239" t="b">
         <v>0</v>
       </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
@@ -31742,16 +31775,16 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112959278</t>
+          <t>https://artportalen.se/Sighting/136175493</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>134063381</v>
+        <v>136898299</v>
       </c>
       <c r="B240" t="n">
-        <v>99472</v>
+        <v>98215</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -31759,16 +31792,16 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>222812</v>
+        <v>221945</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -31777,21 +31810,16 @@
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Murmossen kantzon norra delen, Ramnäs , Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>560964</v>
+        <v>560955</v>
       </c>
       <c r="R240" t="n">
-        <v>6627632</v>
+        <v>6627957</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -31818,22 +31846,22 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -31864,16 +31892,16 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134063381</t>
+          <t>https://artportalen.se/Sighting/136898299</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>5979250</v>
+        <v>112959278</v>
       </c>
       <c r="B241" t="n">
-        <v>99038</v>
+        <v>97986</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -31881,44 +31909,42 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>560984</v>
+        <v>561019</v>
       </c>
       <c r="R241" t="n">
-        <v>6627735</v>
+        <v>6627490</v>
       </c>
       <c r="S241" t="n">
         <v>25</v>
@@ -31945,12 +31971,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -31959,38 +31985,34 @@
       <c r="AE241" t="b">
         <v>0</v>
       </c>
+      <c r="AF241" t="inlineStr"/>
       <c r="AG241" t="b">
         <v>0</v>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
-        </is>
       </c>
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979250</t>
+          <t>https://artportalen.se/Sighting/112959278</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>5979251</v>
+        <v>134063381</v>
       </c>
       <c r="B242" t="n">
-        <v>99038</v>
+        <v>99472</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -31998,47 +32020,42 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>223597</v>
+        <v>222812</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>560967</v>
+        <v>560964</v>
       </c>
       <c r="R242" t="n">
-        <v>6627698</v>
+        <v>6627632</v>
       </c>
       <c r="S242" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32062,12 +32079,22 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -32079,32 +32106,32 @@
       <c r="AG242" t="b">
         <v>0</v>
       </c>
-      <c r="AI242" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979251</t>
+          <t>https://artportalen.se/Sighting/134063381</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>5979254</v>
+        <v>5979250</v>
       </c>
       <c r="B243" t="n">
         <v>99038</v>
@@ -32130,7 +32157,7 @@
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -32149,10 +32176,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>560937</v>
+        <v>560984</v>
       </c>
       <c r="R243" t="n">
-        <v>6627972</v>
+        <v>6627735</v>
       </c>
       <c r="S243" t="n">
         <v>25</v>
@@ -32215,13 +32242,13 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979254</t>
+          <t>https://artportalen.se/Sighting/5979250</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>5979255</v>
+        <v>5979251</v>
       </c>
       <c r="B244" t="n">
         <v>99038</v>
@@ -32247,7 +32274,7 @@
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -32266,10 +32293,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>560943</v>
+        <v>560967</v>
       </c>
       <c r="R244" t="n">
-        <v>6627939</v>
+        <v>6627698</v>
       </c>
       <c r="S244" t="n">
         <v>25</v>
@@ -32331,6 +32358,240 @@
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5979251</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>5979254</v>
+      </c>
+      <c r="B245" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>560937</v>
+      </c>
+      <c r="R245" t="n">
+        <v>6627972</v>
+      </c>
+      <c r="S245" t="n">
+        <v>25</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5979254</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>5979255</v>
+      </c>
+      <c r="B246" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>560943</v>
+      </c>
+      <c r="R246" t="n">
+        <v>6627939</v>
+      </c>
+      <c r="S246" t="n">
+        <v>25</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5979255</t>
         </is>
@@ -32581,6 +32842,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>136898299</v>
       </c>
       <c r="B244" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>136898299</v>
       </c>
       <c r="B249" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>136898299</v>
       </c>
       <c r="B249" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>136898299</v>
       </c>
       <c r="B249" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -32925,7 +32925,7 @@
         <v>136898299</v>
       </c>
       <c r="B249" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>136898299</v>
       </c>
       <c r="B249" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>137074712</v>
       </c>
       <c r="B78" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>137074842</v>
       </c>
       <c r="B147" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>136656184</v>
       </c>
       <c r="B212" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>136948211</v>
       </c>
       <c r="B213" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>137082027</v>
       </c>
       <c r="B214" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>136656321</v>
       </c>
       <c r="B220" t="n">
-        <v>56889</v>
+        <v>56902</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>136898299</v>
       </c>
       <c r="B249" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>137074712</v>
       </c>
       <c r="B78" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>137074842</v>
       </c>
       <c r="B147" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>137038589</v>
       </c>
       <c r="B200" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>136656184</v>
       </c>
       <c r="B212" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>136948211</v>
       </c>
       <c r="B213" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>137082027</v>
       </c>
       <c r="B214" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>136656321</v>
       </c>
       <c r="B220" t="n">
-        <v>56902</v>
+        <v>56904</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>136898299</v>
       </c>
       <c r="B249" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -10036,11 +10036,7 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skogsmursskogen, Ramnäs, Skogsmuren, Ramnäs, Vstm, Vstm</t>
@@ -19563,11 +19559,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
@@ -26434,11 +26426,7 @@
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Salsmosseskogen, Ramnäs, Salsmosseskogen, Ramnäs, Vstm</t>
@@ -28103,11 +28091,7 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -28247,11 +28231,7 @@
       </c>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -28383,11 +28363,7 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -29231,11 +29207,7 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>136898299</v>
       </c>
       <c r="B249" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>137302417</v>
       </c>
       <c r="B65" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>136898299</v>
       </c>
       <c r="B250" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>137303230</v>
       </c>
       <c r="B251" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>137303588</v>
       </c>
       <c r="B252" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>137302994</v>
       </c>
       <c r="B255" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>137302417</v>
       </c>
       <c r="B65" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>137074712</v>
       </c>
       <c r="B79" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>137074842</v>
       </c>
       <c r="B148" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>136948211</v>
       </c>
       <c r="B214" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>137082027</v>
       </c>
       <c r="B215" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>136898299</v>
       </c>
       <c r="B250" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>137303230</v>
       </c>
       <c r="B251" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>137303588</v>
       </c>
       <c r="B252" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>137302994</v>
       </c>
       <c r="B255" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>137302417</v>
       </c>
       <c r="B65" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>136898299</v>
       </c>
       <c r="B250" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>137303230</v>
       </c>
       <c r="B251" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>137303588</v>
       </c>
       <c r="B252" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>137302994</v>
       </c>
       <c r="B255" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>137302417</v>
       </c>
       <c r="B65" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>137074712</v>
       </c>
       <c r="B79" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>137074842</v>
       </c>
       <c r="B148" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>136898299</v>
       </c>
       <c r="B250" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>137303230</v>
       </c>
       <c r="B251" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>137303588</v>
       </c>
       <c r="B252" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>137302994</v>
       </c>
       <c r="B255" t="n">
-        <v>104138</v>
+        <v>104144</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -33620,7 +33620,7 @@
         <v>137302994</v>
       </c>
       <c r="B255" t="n">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>136820919</v>
       </c>
       <c r="B38" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>137302417</v>
       </c>
       <c r="B65" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>136898299</v>
       </c>
       <c r="B250" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>137303230</v>
       </c>
       <c r="B251" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>137303588</v>
       </c>
       <c r="B252" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>137302994</v>
       </c>
       <c r="B255" t="n">
-        <v>104145</v>
+        <v>104157</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>137302417</v>
       </c>
       <c r="B65" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>136898299</v>
       </c>
       <c r="B250" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>137303230</v>
       </c>
       <c r="B251" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>137303588</v>
       </c>
       <c r="B252" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>137302994</v>
       </c>
       <c r="B255" t="n">
-        <v>104157</v>
+        <v>104158</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>137302417</v>
       </c>
       <c r="B65" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>136898299</v>
       </c>
       <c r="B250" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>137303230</v>
       </c>
       <c r="B251" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>137303588</v>
       </c>
       <c r="B252" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>137302994</v>
       </c>
       <c r="B255" t="n">
-        <v>104158</v>
+        <v>104161</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -33018,7 +33018,7 @@
         <v>136898299</v>
       </c>
       <c r="B250" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -5194,7 +5194,7 @@
         <v>137037917</v>
       </c>
       <c r="B39" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>137037395</v>
       </c>
       <c r="B61" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>137038242</v>
       </c>
       <c r="B62" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>137074299</v>
       </c>
       <c r="B63" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>137074398</v>
       </c>
       <c r="B64" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>137302417</v>
       </c>
       <c r="B65" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>137074712</v>
       </c>
       <c r="B79" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>137074842</v>
       </c>
       <c r="B148" t="n">
-        <v>58471</v>
+        <v>58474</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>136948211</v>
       </c>
       <c r="B214" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>137082027</v>
       </c>
       <c r="B215" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>136898299</v>
       </c>
       <c r="B250" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>137303230</v>
       </c>
       <c r="B251" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>137303588</v>
       </c>
       <c r="B252" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>137302994</v>
       </c>
       <c r="B255" t="n">
-        <v>104161</v>
+        <v>104166</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
